--- a/Source Files/Excel version of input data.xlsx
+++ b/Source Files/Excel version of input data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\holden.coffman\Documents\GitHub\CSCI-101-final-project\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{246C5FD9-12B6-449C-A9F4-E551D110283B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80280702-816D-4BAE-A76C-85DE3EEFB1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B8A65AAE-0BB4-4BA0-808E-76381CD3619D}"/>
   </bookViews>
@@ -446,10 +446,10 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -457,73 +457,73 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -534,73 +534,73 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -611,73 +611,73 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -688,29 +688,29 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -721,29 +721,29 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
@@ -754,29 +754,29 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -787,29 +787,29 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -820,29 +820,29 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
@@ -853,29 +853,29 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -886,21 +886,21 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>6</v>
@@ -908,18 +908,18 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
@@ -930,13 +930,13 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
@@ -952,21 +952,21 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>6</v>
@@ -974,73 +974,73 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C54" t="s">
         <v>3</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
         <v>3</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
@@ -1051,84 +1051,84 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
         <v>3</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
         <v>3</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
         <v>4</v>
@@ -1139,139 +1139,139 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
         <v>4</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C72" t="s">
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C75" t="s">
         <v>3</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
         <v>3</v>
@@ -1282,51 +1282,51 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C80" t="s">
         <v>3</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
         <v>3</v>
@@ -1337,65 +1337,65 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C84" t="s">
         <v>3</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C85" t="s">
         <v>4</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C86" t="s">
         <v>3</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C87" t="s">
         <v>3</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C88" t="s">
         <v>3</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C89" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89">
         <v>5</v>
@@ -1403,65 +1403,65 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
         <v>3</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C93" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C94" t="s">
         <v>3</v>
       </c>
       <c r="D94">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C95" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95">
         <v>5</v>
@@ -1475,265 +1475,265 @@
         <v>4</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C97" t="s">
         <v>3</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
         <v>3</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
         <v>3</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C101" t="s">
         <v>3</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
         <v>3</v>
       </c>
       <c r="D102">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C104" t="s">
         <v>3</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C105" t="s">
         <v>3</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
         <v>3</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C108" t="s">
         <v>3</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C109" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="C111" t="s">
         <v>3</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C112" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C113" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C114" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C115" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C116" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C117" t="s">
         <v>3</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C118" t="s">
         <v>3</v>
       </c>
       <c r="D118">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C119" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C120" t="s">
         <v>3</v>
@@ -1744,40 +1744,40 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C121" t="s">
         <v>3</v>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C122" t="s">
         <v>4</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C123" t="s">
         <v>3</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C124" t="s">
         <v>3</v>
@@ -1788,51 +1788,51 @@
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C125" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C126" t="s">
         <v>3</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C127" t="s">
         <v>3</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C128" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C129" t="s">
         <v>4</v>
@@ -1843,128 +1843,128 @@
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C130" t="s">
         <v>3</v>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C131" t="s">
         <v>3</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C132" t="s">
         <v>3</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C133" t="s">
         <v>3</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C134" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C135" t="s">
         <v>4</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C136" t="s">
         <v>3</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C137" t="s">
         <v>3</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C138" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C139" t="s">
         <v>3</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C141" t="s">
         <v>3</v>
@@ -1975,51 +1975,51 @@
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C143" t="s">
         <v>3</v>
       </c>
       <c r="D143">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C145" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C146" t="s">
         <v>3</v>
@@ -2030,51 +2030,51 @@
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C147" t="s">
         <v>3</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C148" t="s">
         <v>4</v>
       </c>
       <c r="D148">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="C149" t="s">
         <v>3</v>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C150" t="s">
         <v>3</v>
       </c>
       <c r="D150">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C151" t="s">
         <v>4</v>
@@ -2085,32 +2085,32 @@
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C152" t="s">
         <v>3</v>
       </c>
       <c r="D152">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="C153" t="s">
         <v>3</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C154" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -2118,40 +2118,40 @@
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C155" t="s">
         <v>3</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C156" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C157" t="s">
         <v>3</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C158" t="s">
         <v>3</v>
@@ -2162,40 +2162,40 @@
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C160" t="s">
         <v>3</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C161" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C162" t="s">
         <v>4</v>
@@ -2206,84 +2206,84 @@
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C163" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C164" t="s">
         <v>3</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C165" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C166" t="s">
         <v>3</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C167" t="s">
         <v>3</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C168" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C169" t="s">
         <v>3</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C170" t="s">
         <v>3</v>
@@ -2294,73 +2294,73 @@
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C171" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C172" t="s">
         <v>3</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C173" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C174" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C175" t="s">
         <v>3</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C176" t="s">
         <v>3</v>
       </c>
       <c r="D176">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C177" t="s">
         <v>3</v>
@@ -2371,65 +2371,65 @@
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C178" t="s">
         <v>4</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
         <v>3</v>
       </c>
       <c r="D180">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C182" t="s">
         <v>3</v>
       </c>
       <c r="D182">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C183" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D183">
         <v>3</v>
@@ -2437,84 +2437,84 @@
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D184">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="C186" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C187" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D187">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C188" t="s">
         <v>3</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="C189" t="s">
         <v>3</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="C190" t="s">
         <v>3</v>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C191" t="s">
         <v>3</v>
@@ -2525,87 +2525,87 @@
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C192" t="s">
         <v>3</v>
       </c>
       <c r="D192">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B193">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C193" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B194">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C194" t="s">
         <v>3</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B195">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C195" t="s">
         <v>3</v>
       </c>
       <c r="D195">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B196">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C196" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D196">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B197">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C197" t="s">
         <v>3</v>
       </c>
       <c r="D197">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B198">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C198" t="s">
         <v>3</v>
       </c>
       <c r="D198">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B199">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C199" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D199">
         <v>2</v>
@@ -2613,73 +2613,73 @@
     </row>
     <row r="200" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B200">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C200" t="s">
         <v>3</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B201">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C201" t="s">
         <v>3</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B202">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C202" t="s">
         <v>3</v>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B203">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C203" t="s">
         <v>4</v>
       </c>
       <c r="D203">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B204">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C204" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D204">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B205">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C205" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B206">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C206" t="s">
         <v>4</v>
@@ -2690,216 +2690,216 @@
     </row>
     <row r="207" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B207">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C207" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B208">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C208" t="s">
         <v>3</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B209">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C209" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D209">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B210">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C210" t="s">
         <v>3</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B211">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C211" t="s">
         <v>3</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B212">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C212" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B213">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C213" t="s">
         <v>3</v>
       </c>
       <c r="D213">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B214">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C214" t="s">
         <v>3</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B215">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C215" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B216">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C216" t="s">
         <v>3</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B217">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C217" t="s">
         <v>3</v>
       </c>
       <c r="D217">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B218">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C218" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B219">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C219" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D219">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B220">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C220" t="s">
         <v>3</v>
       </c>
       <c r="D220">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B221">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C221" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B222">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C222" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B223">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C223" t="s">
         <v>3</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B224">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D224">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B225">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C225" t="s">
         <v>3</v>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B226">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C226" t="s">
         <v>3</v>
@@ -2910,54 +2910,54 @@
     </row>
     <row r="227" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B227">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="C227" t="s">
         <v>3</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B228">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C228" t="s">
         <v>4</v>
       </c>
       <c r="D228">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B229">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C229" t="s">
         <v>3</v>
       </c>
       <c r="D229">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B230">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C230" t="s">
         <v>3</v>
       </c>
       <c r="D230">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B231">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="C231" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D231">
         <v>2</v>
@@ -2965,106 +2965,106 @@
     </row>
     <row r="232" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B232">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C232" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B233">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B234">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C234" t="s">
         <v>4</v>
       </c>
       <c r="D234">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B235">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C235" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D235">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B236">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C236" t="s">
         <v>3</v>
       </c>
       <c r="D236">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B237">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C237" t="s">
         <v>3</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B238">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C238" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D238">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B239">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C239" t="s">
         <v>3</v>
       </c>
       <c r="D239">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B240">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C240" t="s">
         <v>3</v>
       </c>
       <c r="D240">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B241">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C241" t="s">
         <v>3</v>
@@ -3075,57 +3075,57 @@
     </row>
     <row r="242" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B242">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C242" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B243">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C243" t="s">
         <v>3</v>
       </c>
       <c r="D243">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B244">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C244" t="s">
         <v>3</v>
       </c>
       <c r="D244">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B245">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C245" t="s">
         <v>3</v>
       </c>
       <c r="D245">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B246">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C246" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D246">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="2:4" x14ac:dyDescent="0.25">
@@ -3136,12 +3136,12 @@
         <v>3</v>
       </c>
       <c r="D247">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B248">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C248" t="s">
         <v>3</v>
@@ -3152,73 +3152,73 @@
     </row>
     <row r="249" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B249">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C249" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B250">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C250" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D250">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B251">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C251" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D251">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B252">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C252" t="s">
         <v>4</v>
       </c>
       <c r="D252">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B253">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C253" t="s">
         <v>3</v>
       </c>
       <c r="D253">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B254">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C254" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D254">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B255">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C255" t="s">
         <v>4</v>
@@ -3229,117 +3229,117 @@
     </row>
     <row r="256" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B256">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C256" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B257">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C257" t="s">
         <v>3</v>
       </c>
       <c r="D257">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B258">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C258" t="s">
         <v>3</v>
       </c>
       <c r="D258">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B259">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C259" t="s">
         <v>3</v>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B260">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C260" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D260">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B261">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C261" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D261">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B262">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C262" t="s">
         <v>3</v>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B263">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C263" t="s">
         <v>3</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B264">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C264" t="s">
         <v>3</v>
       </c>
       <c r="D264">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B265">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="C265" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D265">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B266">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C266" t="s">
         <v>3</v>
@@ -3350,40 +3350,40 @@
     </row>
     <row r="267" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B267">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C267" t="s">
         <v>3</v>
       </c>
       <c r="D267">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B268">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="C268" t="s">
         <v>4</v>
       </c>
       <c r="D268">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B269">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B270">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C270" t="s">
         <v>3</v>
@@ -3394,29 +3394,29 @@
     </row>
     <row r="271" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B271">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C271" t="s">
         <v>3</v>
       </c>
       <c r="D271">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B272">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="C272" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D272">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B273">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="C273" t="s">
         <v>3</v>
@@ -3427,43 +3427,43 @@
     </row>
     <row r="274" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B274">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C274" t="s">
         <v>3</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B275">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="C275" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B276">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C276" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D276">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B277">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="C277" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="278" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B278">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C278" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -3482,18 +3482,18 @@
     </row>
     <row r="279" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B279">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C279" t="s">
         <v>3</v>
       </c>
       <c r="D279">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B280">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C280" t="s">
         <v>3</v>
@@ -3504,21 +3504,21 @@
     </row>
     <row r="281" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B281">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C281" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D281">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B282">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C282" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -3526,183 +3526,183 @@
     </row>
     <row r="283" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B283">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C283" t="s">
         <v>3</v>
       </c>
       <c r="D283">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B284">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C284" t="s">
         <v>3</v>
       </c>
       <c r="D284">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B285">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C285" t="s">
         <v>3</v>
       </c>
       <c r="D285">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B286">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C286" t="s">
         <v>3</v>
       </c>
       <c r="D286">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B287">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C287" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D287">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B288">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C288" t="s">
         <v>3</v>
       </c>
       <c r="D288">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B289">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C289" t="s">
         <v>3</v>
       </c>
       <c r="D289">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B290">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C290" t="s">
         <v>3</v>
       </c>
       <c r="D290">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B291">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C291" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D291">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B292">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C292" t="s">
         <v>3</v>
       </c>
       <c r="D292">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B293">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C293" t="s">
         <v>3</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B294">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C294" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D294">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B295">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C295" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D295">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B296">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C296" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D296">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B297">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C297" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D297">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B298">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C298" t="s">
         <v>3</v>
       </c>
       <c r="D298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B299">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C299" t="s">
         <v>3</v>
@@ -3713,43 +3713,43 @@
     </row>
     <row r="300" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B300">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C300" t="s">
         <v>3</v>
       </c>
       <c r="D300">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B301">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C301" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D301">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B302">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C302" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B303">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C303" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -3757,18 +3757,18 @@
     </row>
     <row r="304" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B304">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C304" t="s">
         <v>3</v>
       </c>
       <c r="D304">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B305">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C305" t="s">
         <v>3</v>
@@ -3779,18 +3779,18 @@
     </row>
     <row r="306" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B306">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C306" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D306">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B307">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="C307" t="s">
         <v>3</v>
@@ -3801,21 +3801,21 @@
     </row>
     <row r="308" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B308">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="C308" t="s">
         <v>3</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B309">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="C309" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D309">
         <v>0</v>
@@ -3823,18 +3823,18 @@
     </row>
     <row r="310" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B310">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C310" t="s">
         <v>3</v>
       </c>
       <c r="D310">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B311">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C311" t="s">
         <v>3</v>
@@ -3845,18 +3845,18 @@
     </row>
     <row r="312" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B312">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C312" t="s">
         <v>3</v>
       </c>
       <c r="D312">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B313">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="C313" t="s">
         <v>3</v>
@@ -3867,43 +3867,43 @@
     </row>
     <row r="314" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B314">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="C314" t="s">
         <v>3</v>
       </c>
       <c r="D314">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B315">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="C315" t="s">
         <v>3</v>
       </c>
       <c r="D315">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B316">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C316" t="s">
         <v>3</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B317">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="C317" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -3911,73 +3911,73 @@
     </row>
     <row r="318" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B318">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="C318" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B319">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C319" t="s">
         <v>3</v>
       </c>
       <c r="D319">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B320">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="C320" t="s">
         <v>3</v>
       </c>
       <c r="D320">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B321">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="C321" t="s">
         <v>3</v>
       </c>
       <c r="D321">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B322">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C322" t="s">
         <v>3</v>
       </c>
       <c r="D322">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B323">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="C323" t="s">
         <v>3</v>
       </c>
       <c r="D323">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B324">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="C324" t="s">
         <v>4</v>
@@ -3988,118 +3988,118 @@
     </row>
     <row r="325" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B325">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="C325" t="s">
         <v>3</v>
       </c>
       <c r="D325">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B326">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="C326" t="s">
         <v>3</v>
       </c>
       <c r="D326">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B327">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="C327" t="s">
         <v>3</v>
       </c>
       <c r="D327">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B328">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="C328" t="s">
         <v>3</v>
       </c>
       <c r="D328">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B329">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="C329" t="s">
         <v>3</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B330">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="C330" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D330">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B331">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="C331" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D331">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B332">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="C332" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D332">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B333">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="C333" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D333">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B334">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:D334" xr:uid="{BD37414A-3752-4578-A9ED-7A13CB342DF4}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D334">
-      <sortCondition ref="B2:B334"/>
+      <sortCondition descending="1" ref="D2:D334"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
